--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,87 +421,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ngay_cong_bo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>linh_vuc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>loai_hinh</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>trang_thai_xep_hang</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>loai_y_kien</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ky_han</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ket_qua_xep_hang</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>trien_vong</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ma_trai_phieu</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>bao_cao_vi</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>bao_cao_en</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>link_to_chuc_phat_hanh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>issuer_id</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>to_chuc_xhtn</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>thoi_gian_scrape</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ngay_cong_bo_dt</t>
         </is>
@@ -589,10 +577,10 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="n">
         <v>46281</v>
       </c>
     </row>
@@ -658,10 +646,10 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>46276</v>
       </c>
     </row>
@@ -735,10 +723,10 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="n">
         <v>46269</v>
       </c>
     </row>
@@ -812,10 +800,10 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>46260</v>
       </c>
     </row>
@@ -893,10 +881,10 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>46227</v>
       </c>
     </row>
@@ -970,10 +958,10 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>46227</v>
       </c>
     </row>
@@ -1051,10 +1039,10 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>46226</v>
       </c>
     </row>
@@ -1128,10 +1116,10 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="n">
         <v>46226</v>
       </c>
     </row>
@@ -1205,10 +1193,10 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1286,10 +1274,10 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -1359,10 +1347,10 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -1428,10 +1416,10 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -1497,10 +1485,10 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="n">
         <v>46197</v>
       </c>
     </row>
@@ -1574,10 +1562,10 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>46196</v>
       </c>
     </row>
@@ -1643,10 +1631,10 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q16" s="1" t="n">
         <v>46196</v>
       </c>
     </row>
@@ -1712,10 +1700,10 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>46190</v>
       </c>
     </row>
@@ -1793,10 +1781,10 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q18" s="1" t="n">
         <v>46189</v>
       </c>
     </row>
@@ -1870,10 +1858,10 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>46189</v>
       </c>
     </row>
@@ -1939,10 +1927,10 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="n">
         <v>46189</v>
       </c>
     </row>
@@ -2012,10 +2000,10 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>46184</v>
       </c>
     </row>
@@ -2089,10 +2077,10 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>46183</v>
       </c>
     </row>
@@ -2158,10 +2146,10 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>46178</v>
       </c>
     </row>
@@ -2227,10 +2215,10 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>46177</v>
       </c>
     </row>
@@ -2296,10 +2284,10 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>46174</v>
       </c>
     </row>
@@ -2373,10 +2361,10 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>46167</v>
       </c>
     </row>
@@ -2450,10 +2438,10 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>46164</v>
       </c>
     </row>
@@ -2519,10 +2507,10 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>46163</v>
       </c>
     </row>
@@ -2592,10 +2580,10 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>46157</v>
       </c>
     </row>
@@ -2669,10 +2657,10 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>46157</v>
       </c>
     </row>
@@ -2746,10 +2734,10 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q31" s="1" t="n">
         <v>46156</v>
       </c>
     </row>
@@ -2827,10 +2815,10 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q32" s="1" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2904,10 +2892,10 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q33" s="1" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2977,10 +2965,10 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q34" s="1" t="n">
         <v>46154</v>
       </c>
     </row>
@@ -3054,10 +3042,10 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q35" s="1" t="n">
         <v>46150</v>
       </c>
     </row>
@@ -3123,10 +3111,10 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q36" s="1" t="n">
         <v>46136</v>
       </c>
     </row>
@@ -3196,10 +3184,10 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q37" s="1" t="n">
         <v>46134</v>
       </c>
     </row>
@@ -3273,10 +3261,10 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q38" s="1" t="n">
         <v>46134</v>
       </c>
     </row>
@@ -3350,10 +3338,10 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q39" s="1" t="n">
         <v>46134</v>
       </c>
     </row>
@@ -3419,10 +3407,10 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q40" s="1" t="n">
         <v>46133</v>
       </c>
     </row>
@@ -3488,10 +3476,10 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q41" s="1" t="n">
         <v>46133</v>
       </c>
     </row>
@@ -3565,10 +3553,10 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="n">
         <v>46128</v>
       </c>
     </row>
@@ -3634,10 +3622,10 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q43" s="1" t="n">
         <v>46122</v>
       </c>
     </row>
@@ -3711,10 +3699,10 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q44" s="1" t="n">
         <v>46120</v>
       </c>
     </row>
@@ -3780,10 +3768,10 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q45" s="1" t="n">
         <v>46115</v>
       </c>
     </row>
@@ -3849,10 +3837,10 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="n">
         <v>46114</v>
       </c>
     </row>
@@ -3918,10 +3906,10 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q47" s="1" t="n">
         <v>46107</v>
       </c>
     </row>
@@ -3995,10 +3983,10 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q48" s="1" t="n">
         <v>46094</v>
       </c>
     </row>
@@ -4064,10 +4052,10 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q49" s="1" t="n">
         <v>46052</v>
       </c>
     </row>
@@ -4141,10 +4129,10 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q50" s="1" t="n">
         <v>46029</v>
       </c>
     </row>
@@ -4218,10 +4206,10 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="n">
         <v>46028</v>
       </c>
     </row>
@@ -4287,10 +4275,10 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -4368,10 +4356,10 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q53" s="1" t="n">
         <v>46015</v>
       </c>
     </row>
@@ -4445,10 +4433,10 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q54" s="1" t="n">
         <v>46015</v>
       </c>
     </row>
@@ -4522,10 +4510,10 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q55" s="1" t="n">
         <v>46015</v>
       </c>
     </row>
@@ -4599,10 +4587,10 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="n">
         <v>46014</v>
       </c>
     </row>
@@ -4676,10 +4664,10 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q57" s="1" t="n">
         <v>46008</v>
       </c>
     </row>
@@ -4753,10 +4741,10 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="n">
         <v>46007</v>
       </c>
     </row>
@@ -4826,10 +4814,10 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q59" s="1" t="n">
         <v>46003</v>
       </c>
     </row>
@@ -4899,10 +4887,10 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q60" s="1" t="n">
         <v>46003</v>
       </c>
     </row>
@@ -4968,10 +4956,10 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q61" s="1" t="n">
         <v>46003</v>
       </c>
     </row>
@@ -5041,10 +5029,10 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q62" s="1" t="n">
         <v>46003</v>
       </c>
     </row>
@@ -5118,10 +5106,10 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q63" s="1" t="n">
         <v>46000</v>
       </c>
     </row>
@@ -5187,10 +5175,10 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q64" s="1" t="n">
         <v>45996</v>
       </c>
     </row>
@@ -5264,10 +5252,10 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q65" s="1" t="n">
         <v>45996</v>
       </c>
     </row>
@@ -5341,10 +5329,10 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q66" s="1" t="n">
         <v>45992</v>
       </c>
     </row>
@@ -5410,10 +5398,10 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q67" s="1" t="n">
         <v>45982</v>
       </c>
     </row>
@@ -5479,10 +5467,10 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q68" s="1" t="n">
         <v>45975</v>
       </c>
     </row>
@@ -5548,10 +5536,10 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q69" s="1" t="n">
         <v>45975</v>
       </c>
     </row>
@@ -5617,10 +5605,10 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q70" s="1" t="n">
         <v>45975</v>
       </c>
     </row>
@@ -5686,10 +5674,10 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q71" s="1" t="n">
         <v>45975</v>
       </c>
     </row>
@@ -5755,10 +5743,10 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q72" s="1" t="n">
         <v>45969</v>
       </c>
     </row>
@@ -5824,10 +5812,10 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q73" s="1" t="n">
         <v>45954</v>
       </c>
     </row>
@@ -5901,10 +5889,10 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q74" s="1" t="n">
         <v>45952</v>
       </c>
     </row>
@@ -5970,10 +5958,10 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q75" s="1" t="n">
         <v>45952</v>
       </c>
     </row>
@@ -6047,10 +6035,10 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q76" s="1" t="n">
         <v>45951</v>
       </c>
     </row>
@@ -6124,10 +6112,10 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q77" s="1" t="n">
         <v>45933</v>
       </c>
     </row>
@@ -6201,10 +6189,10 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q78" s="1" t="n">
         <v>45932</v>
       </c>
     </row>
@@ -6278,10 +6266,10 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q79" s="1" t="n">
         <v>45926</v>
       </c>
     </row>
@@ -6355,10 +6343,10 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q80" s="1" t="n">
         <v>45916</v>
       </c>
     </row>
@@ -6432,10 +6420,10 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q81" s="1" t="n">
         <v>45905</v>
       </c>
     </row>
@@ -6509,10 +6497,10 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q82" s="1" t="n">
         <v>45870</v>
       </c>
     </row>
@@ -6586,10 +6574,10 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q83" s="1" t="n">
         <v>45839</v>
       </c>
     </row>
@@ -6667,10 +6655,10 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q84" s="1" t="n">
         <v>45820</v>
       </c>
     </row>
@@ -6748,10 +6736,10 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q85" s="1" t="n">
         <v>45820</v>
       </c>
     </row>
@@ -6829,10 +6817,10 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q86" s="1" t="n">
         <v>45820</v>
       </c>
     </row>
@@ -6906,10 +6894,10 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q87" s="1" t="n">
         <v>45820</v>
       </c>
     </row>
@@ -6975,10 +6963,10 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q88" s="1" t="n">
         <v>45812</v>
       </c>
     </row>
@@ -7048,10 +7036,10 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q89" s="1" t="n">
         <v>45806</v>
       </c>
     </row>
@@ -7125,10 +7113,10 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q90" s="1" t="n">
         <v>45798</v>
       </c>
     </row>
@@ -7202,10 +7190,10 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q91" s="1" t="n">
         <v>45792</v>
       </c>
     </row>
@@ -7279,10 +7267,10 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q92" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q92" s="1" t="n">
         <v>45792</v>
       </c>
     </row>
@@ -7356,10 +7344,10 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q93" s="1" t="n">
         <v>45792</v>
       </c>
     </row>
@@ -7433,10 +7421,10 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q94" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q94" s="1" t="n">
         <v>45791</v>
       </c>
     </row>
@@ -7510,10 +7498,10 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q95" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q95" s="1" t="n">
         <v>45785</v>
       </c>
     </row>
@@ -7579,10 +7567,10 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q96" s="1" t="n">
         <v>45772</v>
       </c>
     </row>
@@ -7656,10 +7644,10 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q97" s="1" t="n">
         <v>45769</v>
       </c>
     </row>
@@ -7725,10 +7713,10 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q98" s="1" t="n">
         <v>45768</v>
       </c>
     </row>
@@ -7794,10 +7782,10 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q99" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q99" s="1" t="n">
         <v>45732</v>
       </c>
     </row>
@@ -7871,10 +7859,10 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q100" s="1" t="n">
         <v>45630</v>
       </c>
     </row>
@@ -7940,10 +7928,10 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q101" s="1" t="n">
         <v>45625</v>
       </c>
     </row>
@@ -8009,10 +7997,10 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q102" s="1" t="n">
         <v>45617</v>
       </c>
     </row>
@@ -8078,10 +8066,10 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q103" s="1" t="n">
         <v>45611</v>
       </c>
     </row>
@@ -8147,10 +8135,10 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q104" s="1" t="n">
         <v>45604</v>
       </c>
     </row>
@@ -8224,10 +8212,10 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q105" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q105" s="1" t="n">
         <v>45590</v>
       </c>
     </row>
@@ -8301,10 +8289,10 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q106" s="1" t="n">
         <v>45586</v>
       </c>
     </row>
@@ -8378,10 +8366,10 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q107" s="1" t="n">
         <v>45551</v>
       </c>
     </row>
@@ -8455,10 +8443,10 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q108" s="1" t="n">
         <v>45441</v>
       </c>
     </row>
@@ -8532,10 +8520,10 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q109" s="1" t="n">
         <v>45433</v>
       </c>
     </row>
@@ -8609,10 +8597,10 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q110" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q110" s="1" t="n">
         <v>45427</v>
       </c>
     </row>
@@ -8686,10 +8674,10 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 14:37:52</t>
-        </is>
-      </c>
-      <c r="Q111" s="2" t="n">
+          <t>2026-09-18 07:51:12</t>
+        </is>
+      </c>
+      <c r="Q111" s="1" t="n">
         <v>45420</v>
       </c>
     </row>

--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 07:51:12</t>
+          <t>2026-09-18 08:13:27</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:13:27</t>
+          <t>2026-09-18 08:21:17</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:21:17</t>
+          <t>2026-09-18 08:49:51</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 08:49:51</t>
+          <t>2026-09-18 09:05:30</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:05:30</t>
+          <t>2026-09-18 09:22:39</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260918.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-18 09:22:39</t>
+          <t>2026-09-18 13:06:50</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
